--- a/food_beverage_order_forms/022_frozen_meal_order_form--food_beverage_order_forms.xlsx
+++ b/food_beverage_order_forms/022_frozen_meal_order_form--food_beverage_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>customer_info</t>
+          <t>customer_info_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Customer Email</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Customer Phone</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>address_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Address 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1126,7 +1126,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>customer_info_choices</t>
+          <t>customer_info_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>customer_info_choices</t>
+          <t>customer_info_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +1160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>customer_info_choices</t>
+          <t>customer_info_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +1177,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>customer_info_choices</t>
+          <t>customer_info_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>customer_info_choices</t>
+          <t>customer_info_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>customer_info_choices</t>
+          <t>customer_info_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
